--- a/isms-core-framework/A.8-technological-controls/isms-a.8.16-monitoring/WKBK/90_workbooks/ISMS-IMP-A.8.16.3_Coverage_Assessment_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.16-monitoring/WKBK/90_workbooks/ISMS-IMP-A.8.16.3_Coverage_Assessment_20260208.xlsx
@@ -4068,7 +4068,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Primary identity system (AD/Azure AD) monitored</t>
+          <t>Primary identity system (AD/Microsoft Entra ID (formerly Azure AD)) monitored</t>
         </is>
       </c>
       <c r="S27" s="5" t="n"/>
@@ -4272,7 +4272,7 @@
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
     <dataValidation sqref="B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Active Directory,Azure AD,LDAP,SAML IdP,OAuth Provider,Database Auth,Application-Specific,Other"</formula1>
+      <formula1>"Active Directory,Microsoft Entra ID (formerly Azure AD),LDAP,SAML IdP,OAuth Provider,Database Auth,Application-Specific,Other"</formula1>
     </dataValidation>
     <dataValidation sqref="Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 S27 S28 S29 S30 S31 S32 S33 S34 S35 S36 S37 S38 S39 S40 S41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"✅ Compliant,⚠️ Partial,❌ Non-Compliant,N/A"</formula1>
